--- a/activities/04 - Choose and Pilot a Countermeasure/data/A04-Data-Workbook.xlsx
+++ b/activities/04 - Choose and Pilot a Countermeasure/data/A04-Data-Workbook.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v4</t>
+          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v5</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>What actually happened when the chosen countermeasure was piloted for one week. The same 60-customer observation was repeated each day. Used in Step 7 to judge whether the pilot worked, and carried into Lab 5 as the new baseline.</t>
+          <t>What actually happened when the chosen countermeasure was piloted for one week. The same 60-customer observation was repeated each day. Used in Step 7 to judge whether the pilot worked, and carried into Activity 5 as the new baseline.</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Note: Thursday is deliberately bad — the opening staff member was on leave and the restock was missed. That single row is the most important teaching point in the lab: the countermeasure works, but nothing yet HOLDS it in place. That is exactly what Lab 5 (Control) exists to fix.</t>
+          <t>Note: Thursday is deliberately bad — the opening staff member was on leave and the restock was missed. That single row is the most important teaching point in the lab: the countermeasure works, but nothing yet HOLDS it in place. That is exactly what Activity 5 (Control) exists to fix.</t>
         </is>
       </c>
     </row>

--- a/activities/04 - Choose and Pilot a Countermeasure/data/A04-Data-Workbook.xlsx
+++ b/activities/04 - Choose and Pilot a Countermeasure/data/A04-Data-Workbook.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v5</t>
+          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v6</t>
         </is>
       </c>
     </row>

--- a/activities/04 - Choose and Pilot a Countermeasure/data/A04-Data-Workbook.xlsx
+++ b/activities/04 - Choose and Pilot a Countermeasure/data/A04-Data-Workbook.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v6</t>
+          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v7</t>
         </is>
       </c>
     </row>
